--- a/r4-core-131-Gemeindecode/StructureDefinition-at-core-address.xlsx
+++ b/r4-core-131-Gemeindecode/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:27:00+00:00</t>
+    <t>2026-10-13T07:58:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -354,7 +354,7 @@
     <t>Address Municipality Code (Gemeindecode)</t>
   </si>
   <si>
-    <t>HL7® Austria FHIR® Core Extension for the municipality code (Gemeindecode) part of the Austrian address. The municipality key is related to the [municipality key (Gemeindekennziffer)](StructureDefinition-at-core-ext-address-municipalityKey.html). While these two are generally identical, there is one notable exception: in Vienna, the municipality key (Gemeindekennziffer) is consistently 90001, whereas the municipality code (Gemeindecode) varies by district. The current list of values is provided by [Statistik Austria](https://www.statistik.at/verzeichnis/reglisten/gemliste_knz.pdf).</t>
+    <t>HL7® Austria FHIR® Core Extension for the municipality code (Gemeindecode) part of the Austrian address. The municipality code is related to the [municipality key (Gemeindekennziffer)](StructureDefinition-at-core-ext-address-municipalityKey.html). While these two are generally identical, there is one notable exception: in Vienna, the municipality key (Gemeindekennziffer) is consistently 90001, whereas the municipality code (Gemeindecode) varies by district. The current list of values is provided by [Statistik Austria](https://www.statistik.at/verzeichnis/reglisten/gemliste_knz.pdf).</t>
   </si>
   <si>
     <t>Address.extension:municipalityKey</t>
